--- a/docs/design-vi/ACSMS-SCR-025/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_アカウントマスタ登録画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-025/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_アカウントマスタ登録画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật: tạo カテゴリ8 và bổ sung 2 ca (069〜070). 069＝hủy toàn bộ session khi có thay đổi quan trọng về bảo mật (xử lý cho security review 2026-07): đổi mật khẩu/khóa(true)/đổi role/đổi nơi trực thuộc thì hủy; mở khóa・chỉ đổi họ tên/email/ghi chú・cập nhật mà giá trị không đổi thì không hủy; xóa thì hủy vô điều kiện; Redis lỗi thì cập nhật vẫn thành lập và hiển thị thành công. 070＝kiểm tra tên dành riêng `SYSTEM` cho ID đăng nhập (#55719): từ chối `SYSTEM` đơn lẻ và tiền tố `SYSTEM_` bất kể hoa thường, cho phép `SYSTEMS`/`MYSYSTEM`, phòng thủ ở cả DTO lẫn ràng buộc CHECK của DB</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6314,7 +6374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ86"/>
+  <dimension ref="A1:BQ89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -21629,8 +21689,264 @@
       <c r="BP86" s="10" t="n"/>
       <c r="BQ86" s="11" t="n"/>
     </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>Hủy session・Kiểm tra tên dành riêng (Session / Reserved-name)</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="10" t="n"/>
+      <c r="AL87" s="10" t="n"/>
+      <c r="AM87" s="10" t="n"/>
+      <c r="AN87" s="10" t="n"/>
+      <c r="AO87" s="10" t="n"/>
+      <c r="AP87" s="10" t="n"/>
+      <c r="AQ87" s="10" t="n"/>
+      <c r="AR87" s="10" t="n"/>
+      <c r="AS87" s="10" t="n"/>
+      <c r="AT87" s="10" t="n"/>
+      <c r="AU87" s="10" t="n"/>
+      <c r="AV87" s="10" t="n"/>
+      <c r="AW87" s="10" t="n"/>
+      <c r="AX87" s="10" t="n"/>
+      <c r="AY87" s="10" t="n"/>
+      <c r="AZ87" s="10" t="n"/>
+      <c r="BA87" s="10" t="n"/>
+      <c r="BB87" s="10" t="n"/>
+      <c r="BC87" s="10" t="n"/>
+      <c r="BD87" s="10" t="n"/>
+      <c r="BE87" s="10" t="n"/>
+      <c r="BF87" s="10" t="n"/>
+      <c r="BG87" s="10" t="n"/>
+      <c r="BH87" s="10" t="n"/>
+      <c r="BI87" s="10" t="n"/>
+      <c r="BJ87" s="10" t="n"/>
+      <c r="BK87" s="10" t="n"/>
+      <c r="BL87" s="10" t="n"/>
+      <c r="BM87" s="10" t="n"/>
+      <c r="BN87" s="10" t="n"/>
+      <c r="BO87" s="10" t="n"/>
+      <c r="BP87" s="10" t="n"/>
+      <c r="BQ87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="160" customHeight="1">
+      <c r="A88" s="44" t="n">
+        <v>69</v>
+      </c>
+      <c r="B88" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-025-069</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="46" t="inlineStr">
+        <is>
+          <t>Hủy session khi có thay đổi quan trọng về bảo mật (de-provisioning)</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (có quyền `account.update` / `account.delete`)
+・Tài khoản đối tượng B (JA_HONTEN) **đang đăng nhập ở trình duyệt khác** (đang giữ session cookie hợp lệ)
+・Chuẩn bị cả môi trường có thể tạm dừng Redis (dùng cho Bước 8)</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="10" t="n"/>
+      <c r="M88" s="10" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="11" t="n"/>
+      <c r="Q88" s="46" t="inlineStr"/>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="11" t="n"/>
+      <c r="X88" s="46" t="inlineStr"/>
+      <c r="Y88" s="10" t="n"/>
+      <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="10" t="n"/>
+      <c r="AD88" s="11" t="n"/>
+      <c r="AE88" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF88" s="11" t="n"/>
+      <c r="AG88" s="45" t="inlineStr"/>
+      <c r="AH88" s="10" t="n"/>
+      <c r="AI88" s="11" t="n"/>
+      <c r="AJ88" s="45" t="inlineStr"/>
+      <c r="AK88" s="10" t="n"/>
+      <c r="AL88" s="11" t="n"/>
+      <c r="AM88" s="45" t="inlineStr"/>
+      <c r="AN88" s="10" t="n"/>
+      <c r="AO88" s="11" t="n"/>
+      <c r="AP88" s="45" t="inlineStr"/>
+      <c r="AQ88" s="10" t="n"/>
+      <c r="AR88" s="11" t="n"/>
+      <c r="AS88" s="45" t="inlineStr"/>
+      <c r="AT88" s="10" t="n"/>
+      <c r="AU88" s="11" t="n"/>
+      <c r="AV88" s="45" t="inlineStr"/>
+      <c r="AW88" s="10" t="n"/>
+      <c r="AX88" s="11" t="n"/>
+      <c r="AY88" s="45" t="inlineStr"/>
+      <c r="AZ88" s="10" t="n"/>
+      <c r="BA88" s="11" t="n"/>
+      <c r="BB88" s="45" t="inlineStr"/>
+      <c r="BC88" s="10" t="n"/>
+      <c r="BD88" s="11" t="n"/>
+      <c r="BE88" s="45" t="inlineStr"/>
+      <c r="BF88" s="10" t="n"/>
+      <c r="BG88" s="11" t="n"/>
+      <c r="BH88" s="45" t="inlineStr"/>
+      <c r="BI88" s="10" t="n"/>
+      <c r="BJ88" s="11" t="n"/>
+      <c r="BK88" s="46" t="inlineStr"/>
+      <c r="BL88" s="10" t="n"/>
+      <c r="BM88" s="10" t="n"/>
+      <c r="BN88" s="10" t="n"/>
+      <c r="BO88" s="10" t="n"/>
+      <c r="BP88" s="10" t="n"/>
+      <c r="BQ88" s="11" t="n"/>
+    </row>
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="44" t="n">
+        <v>70</v>
+      </c>
+      <c r="B89" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-025-070</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="46" t="inlineStr">
+        <is>
+          <t>Kiểm tra tên dành riêng SYSTEM cho ID đăng nhập (#55719)</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (có quyền `account.create`)
+・Đang mở màn hình đăng ký tài khoản (chế độ tạo mới)</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="11" t="n"/>
+      <c r="Q89" s="46" t="inlineStr"/>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="11" t="n"/>
+      <c r="X89" s="46" t="inlineStr"/>
+      <c r="Y89" s="10" t="n"/>
+      <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="10" t="n"/>
+      <c r="AD89" s="11" t="n"/>
+      <c r="AE89" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF89" s="11" t="n"/>
+      <c r="AG89" s="45" t="inlineStr"/>
+      <c r="AH89" s="10" t="n"/>
+      <c r="AI89" s="11" t="n"/>
+      <c r="AJ89" s="45" t="inlineStr"/>
+      <c r="AK89" s="10" t="n"/>
+      <c r="AL89" s="11" t="n"/>
+      <c r="AM89" s="45" t="inlineStr"/>
+      <c r="AN89" s="10" t="n"/>
+      <c r="AO89" s="11" t="n"/>
+      <c r="AP89" s="45" t="inlineStr"/>
+      <c r="AQ89" s="10" t="n"/>
+      <c r="AR89" s="11" t="n"/>
+      <c r="AS89" s="45" t="inlineStr"/>
+      <c r="AT89" s="10" t="n"/>
+      <c r="AU89" s="11" t="n"/>
+      <c r="AV89" s="45" t="inlineStr"/>
+      <c r="AW89" s="10" t="n"/>
+      <c r="AX89" s="11" t="n"/>
+      <c r="AY89" s="45" t="inlineStr"/>
+      <c r="AZ89" s="10" t="n"/>
+      <c r="BA89" s="11" t="n"/>
+      <c r="BB89" s="45" t="inlineStr"/>
+      <c r="BC89" s="10" t="n"/>
+      <c r="BD89" s="11" t="n"/>
+      <c r="BE89" s="45" t="inlineStr"/>
+      <c r="BF89" s="10" t="n"/>
+      <c r="BG89" s="11" t="n"/>
+      <c r="BH89" s="45" t="inlineStr"/>
+      <c r="BI89" s="10" t="n"/>
+      <c r="BJ89" s="11" t="n"/>
+      <c r="BK89" s="46" t="inlineStr"/>
+      <c r="BL89" s="10" t="n"/>
+      <c r="BM89" s="10" t="n"/>
+      <c r="BN89" s="10" t="n"/>
+      <c r="BO89" s="10" t="n"/>
+      <c r="BP89" s="10" t="n"/>
+      <c r="BQ89" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1229">
+  <mergeCells count="1264">
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -21654,6 +21970,7 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="J75:P75"/>
     <mergeCell ref="AV81:AX81"/>
+    <mergeCell ref="BB88:BD88"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AS67:AU67"/>
@@ -21732,6 +22049,7 @@
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="BK88:BQ88"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="BE39:BG39"/>
@@ -21807,6 +22125,7 @@
     <mergeCell ref="BE76:BG76"/>
     <mergeCell ref="AG76:AI76"/>
     <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B82:D82"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -21817,8 +22136,10 @@
     <mergeCell ref="AS13:AU13"/>
     <mergeCell ref="B85:D85"/>
     <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="BE89:BG89"/>
     <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="X73:AD73"/>
+    <mergeCell ref="BE88:BG88"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="AS25:AU25"/>
     <mergeCell ref="B14:D14"/>
@@ -21838,6 +22159,7 @@
     <mergeCell ref="AS81:AU81"/>
     <mergeCell ref="AV82:AX82"/>
     <mergeCell ref="BE47:BG47"/>
+    <mergeCell ref="AM88:AO88"/>
     <mergeCell ref="AM82:AO82"/>
     <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="BE40:BG40"/>
@@ -21869,6 +22191,7 @@
     <mergeCell ref="X43:AD43"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="J88:P88"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="AS24:AU24"/>
     <mergeCell ref="AE19:AF19"/>
@@ -21894,6 +22217,7 @@
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="E54:I54"/>
+    <mergeCell ref="AS88:AU88"/>
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="E56:I56"/>
@@ -21928,6 +22252,8 @@
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AE28:AF28"/>
     <mergeCell ref="AY86:BA86"/>
+    <mergeCell ref="Q88:W88"/>
+    <mergeCell ref="BB89:BD89"/>
     <mergeCell ref="X80:AD80"/>
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="BB82:BD82"/>
@@ -21986,7 +22312,9 @@
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="BK68:BQ68"/>
+    <mergeCell ref="X89:AD89"/>
     <mergeCell ref="BK67:BQ67"/>
+    <mergeCell ref="X88:AD88"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="AC8:AE8"/>
     <mergeCell ref="AP69:AR69"/>
@@ -22007,6 +22335,7 @@
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="X20:AD20"/>
     <mergeCell ref="BH74:BJ74"/>
+    <mergeCell ref="AP88:AR88"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AP82:AR82"/>
     <mergeCell ref="B42:D42"/>
@@ -22028,6 +22357,7 @@
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
+    <mergeCell ref="BH89:BJ89"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AY68:BA68"/>
@@ -22130,6 +22460,7 @@
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="BB31:BD31"/>
+    <mergeCell ref="E88:I88"/>
     <mergeCell ref="Q32:W32"/>
     <mergeCell ref="E82:I82"/>
     <mergeCell ref="X22:AD22"/>
@@ -22168,9 +22499,11 @@
     <mergeCell ref="AJ77:AL77"/>
     <mergeCell ref="BK84:BQ84"/>
     <mergeCell ref="BK86:BQ86"/>
+    <mergeCell ref="AE88:AF88"/>
     <mergeCell ref="AE82:AF82"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
+    <mergeCell ref="AS89:AU89"/>
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AE83:AF83"/>
@@ -22252,6 +22585,7 @@
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="A26:BQ26"/>
     <mergeCell ref="AY74:BA74"/>
+    <mergeCell ref="AG88:AI88"/>
     <mergeCell ref="AG82:AI82"/>
     <mergeCell ref="AY76:BA76"/>
     <mergeCell ref="BK47:BQ47"/>
@@ -22267,6 +22601,7 @@
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="BK37:BQ37"/>
     <mergeCell ref="AP66:AR66"/>
+    <mergeCell ref="AY89:BA89"/>
     <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
@@ -22307,6 +22642,7 @@
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
+    <mergeCell ref="B89:D89"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="Q51:W51"/>
@@ -22330,8 +22666,10 @@
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="AJ65:AL65"/>
+    <mergeCell ref="AV89:AX89"/>
     <mergeCell ref="J29:P29"/>
     <mergeCell ref="BB17:BD17"/>
+    <mergeCell ref="AM89:AO89"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="BE53:BG53"/>
@@ -22419,6 +22757,7 @@
     <mergeCell ref="BB81:BD81"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="AJ88:AL88"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="Q42:W42"/>
@@ -22530,8 +22869,10 @@
     <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="BH81:BJ81"/>
+    <mergeCell ref="AP89:AR89"/>
     <mergeCell ref="BE11:BG11"/>
     <mergeCell ref="B49:D49"/>
+    <mergeCell ref="BK89:BQ89"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="X52:AD52"/>
@@ -22569,6 +22910,7 @@
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="A87:BQ87"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AV86:AX86"/>
     <mergeCell ref="BE13:BG13"/>
@@ -22654,6 +22996,7 @@
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="E89:I89"/>
     <mergeCell ref="AJ75:AL75"/>
     <mergeCell ref="J74:P74"/>
     <mergeCell ref="J49:P49"/>
@@ -22676,7 +23019,9 @@
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="Q83:W83"/>
+    <mergeCell ref="AG89:AI89"/>
     <mergeCell ref="BB75:BD75"/>
+    <mergeCell ref="J89:P89"/>
     <mergeCell ref="Q85:W85"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="Q78:W78"/>
@@ -22701,6 +23046,7 @@
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="AE89:AF89"/>
     <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="BB58:BD58"/>
     <mergeCell ref="J47:P47"/>
@@ -22727,9 +23073,11 @@
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="BH82:BJ82"/>
+    <mergeCell ref="BH88:BJ88"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AP11:AR11"/>
     <mergeCell ref="BK36:BQ36"/>
+    <mergeCell ref="AY88:BA88"/>
     <mergeCell ref="AS47:AU47"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="BH83:BJ83"/>
@@ -22743,6 +23091,7 @@
     <mergeCell ref="X83:AD83"/>
     <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="Q89:W89"/>
     <mergeCell ref="X85:AD85"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="AE59:AF59"/>
@@ -22794,6 +23143,7 @@
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
+    <mergeCell ref="AV88:AX88"/>
     <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
@@ -22835,6 +23185,7 @@
     <mergeCell ref="X63:AD63"/>
     <mergeCell ref="AE20:AF20"/>
     <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="AJ89:AL89"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="AS45:AU45"/>
@@ -22862,13 +23213,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE60 AE62:AE69 AE71:AE78 AE80:AE86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE60 AE62:AE69 AE71:AE78 AE80:AE86 AE88:AE89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG60 AG62:AG69 AG71:AG78 AG80:AG86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG60 AG62:AG69 AG71:AG78 AG80:AG86 AG88:AG89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV60 AV62:AV69 AV71:AV78 AV80:AV86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV60 AV62:AV69 AV71:AV78 AV80:AV86 AV88:AV89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
